--- a/graph_invariants/results/results.xlsx
+++ b/graph_invariants/results/results.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,66 +413,61 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>g6</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>file_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>graph_index</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>vertex_count</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>edge_count</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>max_deg</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>chromatic_number_of_square</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>prediction</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>conjecture_role</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>timestamp</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>URL</t>
         </is>
@@ -493,133 +476,124 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>F@U^?</t>
+          <t>J??B\rSF~F?</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>list_1448_graphs_1to10.g6</t>
+          <t>list_1124_graphs_11to20.g6</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>131</v>
+        <v>897</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E2" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
-      </c>
-      <c r="H2" t="n">
-        <v>7</v>
+        <v>11</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>TIGHT</t>
+        </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>TIGHT</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>2026-02-04 12:31:02</t>
-        </is>
-      </c>
+          <t>2026-02-05 06:23:50</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HJYucYJ</t>
+          <t>J@QBtjKF~F?</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>list_1448_graphs_1to10.g6</t>
+          <t>list_1124_graphs_11to20.g6</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>546</v>
+        <v>898</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G3" t="n">
-        <v>9</v>
-      </c>
-      <c r="H3" t="n">
-        <v>9</v>
+        <v>11</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>TIGHT</t>
+        </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>TIGHT</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>2026-02-04 12:31:03</t>
-        </is>
-      </c>
+          <t>2026-02-05 06:23:54</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FHU^?</t>
+          <t>KdO_?SFLmu|k</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>list_1448_graphs_1to10.g6</t>
+          <t>list_1124_graphs_11to20.g6</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>829</v>
+        <v>899</v>
       </c>
       <c r="D4" t="n">
+        <v>12</v>
+      </c>
+      <c r="E4" t="n">
+        <v>29</v>
+      </c>
+      <c r="F4" t="n">
         <v>7</v>
       </c>
-      <c r="E4" t="n">
-        <v>10</v>
-      </c>
-      <c r="F4" t="n">
-        <v>3</v>
-      </c>
       <c r="G4" t="n">
-        <v>7</v>
-      </c>
-      <c r="H4" t="n">
-        <v>7</v>
+        <v>12</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>TIGHT</t>
+        </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>TIGHT</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>2026-02-04 12:31:04</t>
-        </is>
-      </c>
+          <t>2026-02-05 06:24:51</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>H?TktNo</t>
+          <t>F@U^?</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -628,77 +602,305 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>860</v>
+        <v>131</v>
       </c>
       <c r="D5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E5" t="n">
         <v>9</v>
       </c>
-      <c r="E5" t="n">
-        <v>16</v>
-      </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>9</v>
-      </c>
-      <c r="H5" t="n">
-        <v>9</v>
+        <v>7</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>TIGHT</t>
+        </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>TIGHT</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2026-02-04 12:31:04</t>
-        </is>
-      </c>
+          <t>2026-02-05 06:23:37</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>HJYucYJ</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>list_1448_graphs_1to10.g6</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>546</v>
+      </c>
+      <c r="D6" t="n">
+        <v>9</v>
+      </c>
+      <c r="E6" t="n">
+        <v>18</v>
+      </c>
+      <c r="F6" t="n">
+        <v>4</v>
+      </c>
+      <c r="G6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>TIGHT</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-02-05 06:23:39</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>FHU^?</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>list_1448_graphs_1to10.g6</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>829</v>
+      </c>
+      <c r="D7" t="n">
+        <v>7</v>
+      </c>
+      <c r="E7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" t="n">
+        <v>7</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>TIGHT</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-02-05 06:23:41</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>H?TktNo</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>list_1448_graphs_1to10.g6</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>860</v>
+      </c>
+      <c r="D8" t="n">
+        <v>9</v>
+      </c>
+      <c r="E8" t="n">
+        <v>16</v>
+      </c>
+      <c r="F8" t="n">
+        <v>4</v>
+      </c>
+      <c r="G8" t="n">
+        <v>9</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>TIGHT</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-02-05 06:23:41</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>I?LiuMkcw</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>list_1448_graphs_1to10.g6</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C9" t="n">
         <v>1078</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D9" t="n">
         <v>10</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E9" t="n">
         <v>21</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F9" t="n">
         <v>5</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G9" t="n">
         <v>10</v>
       </c>
-      <c r="H6" t="n">
-        <v>10</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>TIGHT</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>2026-02-04 12:31:05</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>TIGHT</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-02-05 06:23:43</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>JY_?g\uj]u?</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>list_1124_graphs_11to20.g6</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>900</v>
+      </c>
+      <c r="D10" t="n">
+        <v>11</v>
+      </c>
+      <c r="E10" t="n">
+        <v>26</v>
+      </c>
+      <c r="F10" t="n">
+        <v>6</v>
+      </c>
+      <c r="G10" t="n">
+        <v>11</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>TIGHT</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-02-05 06:24:54</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>KK??GOBB~w}[</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>list_1124_graphs_11to20.g6</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>901</v>
+      </c>
+      <c r="D11" t="n">
+        <v>12</v>
+      </c>
+      <c r="E11" t="n">
+        <v>25</v>
+      </c>
+      <c r="F11" t="n">
+        <v>7</v>
+      </c>
+      <c r="G11" t="n">
+        <v>12</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>TIGHT</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-02-05 06:25:50</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>L?????@?fwB~w}</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>list_1124_graphs_11to20.g6</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>903</v>
+      </c>
+      <c r="D12" t="n">
+        <v>13</v>
+      </c>
+      <c r="E12" t="n">
+        <v>24</v>
+      </c>
+      <c r="F12" t="n">
+        <v>8</v>
+      </c>
+      <c r="G12" t="n">
+        <v>13</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>TIGHT</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-02-05 06:26:57</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
